--- a/artfynd/A 51315-2025 artfynd.xlsx
+++ b/artfynd/A 51315-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129224227</v>
       </c>
       <c r="B2" t="n">
-        <v>97728</v>
+        <v>97738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51315-2025 artfynd.xlsx
+++ b/artfynd/A 51315-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129224227</v>
       </c>
       <c r="B2" t="n">
-        <v>97738</v>
+        <v>97745</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51315-2025 artfynd.xlsx
+++ b/artfynd/A 51315-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129224227</v>
       </c>
       <c r="B2" t="n">
-        <v>97745</v>
+        <v>97747</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51315-2025 artfynd.xlsx
+++ b/artfynd/A 51315-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129224227</v>
       </c>
       <c r="B2" t="n">
-        <v>97747</v>
+        <v>97773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51315-2025 artfynd.xlsx
+++ b/artfynd/A 51315-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129224227</v>
       </c>
       <c r="B2" t="n">
-        <v>97773</v>
+        <v>97774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51315-2025 artfynd.xlsx
+++ b/artfynd/A 51315-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129224227</v>
       </c>
       <c r="B2" t="n">
-        <v>97774</v>
+        <v>97775</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51315-2025 artfynd.xlsx
+++ b/artfynd/A 51315-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129224227</v>
       </c>
       <c r="B2" t="n">
-        <v>97775</v>
+        <v>97779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
